--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_794_Turkey_Black_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_794_Turkey_Black_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R768bdc6853934c75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R2c82e0502fb24777"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf2dc71ff131b43d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R79ceed7442d0446e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R39e9494327aa4191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Re98a743cadba4e62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R591cc48c4f5d4dbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4634c4a3f4884ba0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R92f199c50cee41ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R11817c65d8834de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R8780b465d11949e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd1f8947c5c094267"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ794CommercialTable" displayName="EEZ794CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ794CommercialTable" displayName="EEZ794CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ794FunctionalTable" displayName="EEZ794FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ794FunctionalTable" displayName="EEZ794FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ794ValidationTable" displayName="EEZ794ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ794ValidationTable" displayName="EEZ794ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -3977,7 +3931,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a37f15226414490"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f943b4b5c934d1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3987,20 +3941,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4008,660 +3952,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>268355.5097471848</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>268355.5097471848</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$50,A2,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>34570886.512619324</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>34570886.512619324</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>15033.936922215798</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.359991793983905</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2290.824367117112</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>15033.936922215798</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2290.8282877924603</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$50,A3,'Species'!$U$2:$U$50))</x:f>
-        <x:v>34440167.97829947</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.359991793983905</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2290.824367117112</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>34440109.03511359</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>58.94318588078022</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0000017114692006</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0000017114692006545158</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>4.6902821778</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2167824680682475</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>164.73370571314052</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>4.6902821778</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>168.8881616206533</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$50,A4,'Species'!$U$2:$U$50))</x:f>
-        <x:v>792.1331344907562</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2167824680682475</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>164.73370571314052</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>772.6475639892931</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>19.485570501463144</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.025219222074365</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.025219222074365027</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>347.6906623027</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.3327630599671805</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2151.6075520487043</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>347.6906623027</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2240.451208902624</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$50,A5,'Species'!$U$2:$U$50))</x:f>
-        <x:v>778983.9646802382</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.3327630599671805</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2151.6075520487043</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>748093.854787305</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>30890.109892933164</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0412917573045908</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.04129175730459077</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>159224.67438561848</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.0148113608514238</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>103.46926423517272</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>159224.67438561848</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>106.81613799251876</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$50,A6,'Species'!$U$2:$U$50))</x:f>
-        <x:v>17007764.79098809</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.0148113608514238</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>103.46926423517272</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>16474859.906764895</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>532904.8842231967</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0323465502735094</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.032346550273509495</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>60038.0216073092</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.2628050350088214</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>18.314920380076096</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>60038.0216073092</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>22.63092033779597</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$50,A7,'Species'!$U$2:$U$50))</x:f>
-        <x:v>1358715.6842338878</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.2628050350088214</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>18.314920380076096</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1099591.5855151564</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>259124.09871873143</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2356548577964357</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.2356548577964357</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>16138.668287328499</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.285822470932016</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>193.11787365422336</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>16138.668287328499</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>200.3436329622945</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$50,A8,'Species'!$U$2:$U$50))</x:f>
-        <x:v>3233279.435856763</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.285822470932016</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>193.11787365422336</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3116665.303259726</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>116614.13259703666</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0374163155970164</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.03741631559701637</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>22097.0399608921</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.81024213500587</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>646.0143051731324</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>22097.0399608921</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1014.7322858288766</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$50,A9,'Species'!$U$2:$U$50))</x:f>
-        <x:v>22422579.86956807</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.81024213500587</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>646.0143051731324</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>14275003.916718649</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>8147575.95284942</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.5707582288861661</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.5707582288861661</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>107.352883644</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9200000000000004</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>831.7637711026717</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>107.352883644</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$50,A10,'Species'!$U$2:$U$50))</x:f>
-        <x:v>89292.23933847967</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9200000000000004</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>831.7637711026717</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>89292.23933847978</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>-1.0186340659856796e-10</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>-1.140786784531573e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>5.840805920499999</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.7945587668894367</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>623.1014571741812</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>5.840805920499999</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>687.738622946611</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$50,A11,'Species'!$U$2:$U$50))</x:f>
-        <x:v>4016.9478206630824</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.7945587668894367</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>623.1014571741812</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3639.4146801351344</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>377.53314052794804</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1037345764934734</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.10373457649347337</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>15857.3548337986</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.500000053551329</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>3162.278050097766</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>15857.3548337986</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>3162.278063880962</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$50,A12,'Species'!$U$2:$U$50))</x:f>
-        <x:v>50145365.34209804</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.500000053551329</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>3162.278050097766</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>50145365.12353302</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0.21856502443552017</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0000000043586286</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>4.358628636905637e-9</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R890764b51331458c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c1cd1cda6a94d65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4671,20 +4186,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4692,1146 +4197,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.1355453071</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.27</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1862.0871366628655</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.1355453071</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1862.0871366628655</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$50,A2,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>252.3971727859278</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.27</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1862.0871366628655</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>252.3971727859278</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3.0902515829</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.420876157624829</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2635.5797230525463</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3.0902515829</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2649.5631444505516</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$50,A3,'Species'!$U$2:$U$50))</x:f>
-        <x:v>8187.816701131818</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.420876157624829</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2635.5797230525463</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>8144.604411022276</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>43.212290109542664</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.005305634003668</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.005305634003667815</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>113.69080460340001</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2698295571060947</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>186.13564866952103</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>113.69080460340001</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>231.10099945004023</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$50,A4,'Species'!$U$2:$U$50))</x:f>
-        <x:v>26274.058572124977</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2698295571060947</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>186.13564866952103</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>21161.911662613627</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>5112.14690951135</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2415730200094772</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.24157302000947717</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>339.4558538513</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>339.4558538513</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$50,A5,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>777648.4351306085</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>777648.4351306085</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3879.9030850663003</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.53</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>3388.4415613920273</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3879.9030850663003</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>3388.4415613920273</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$50,A6,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>13146824.867611798</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.53</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>3388.4415613920273</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>13146824.867611798</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>4.4957926835999995</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.711673637779484</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>514.8416076598098</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>4.4957926835999995</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>533.1243505775026</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$50,A7,'Species'!$U$2:$U$50))</x:f>
-        <x:v>2396.8165547753374</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.711673637779484</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>514.8416076598098</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2314.6211329298344</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>82.195421845503</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0355113934959457</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.03551139349594571</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1.3450132368999999</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.071607606862653</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1179.2546756467082</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1.3450132368999999</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1204.5467073780183</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$50,A8,'Species'!$U$2:$U$50))</x:f>
-        <x:v>1620.1312658877453</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.071607606862653</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1179.2546756467082</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>1586.1131484210384</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>34.018117466706826</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0214474720801423</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0214474720801423</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1.9515685345</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.1</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>125.89254117941675</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1.9515685345</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>125.89254117941675</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$50,A9,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>245.68792209399527</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.1</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>125.89254117941675</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>245.68792209399527</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1.2707636485</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.27</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1862.0871366628655</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1.2707636485</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1862.0871366628658</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$50,A10,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2366.2726436106213</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.27</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1862.0871366628655</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>2366.2726436106213</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>15039.4396603784</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.359364028858923</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2287.5154124063906</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>15039.4396603784</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2289.7905788744556</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$50,A11,'Species'!$U$2:$U$50))</x:f>
-        <x:v>34437167.245885305</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.359364028858923</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2287.5154124063906</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>34402950.01707152</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>34217.228813782334</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.000994601590759</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0009946015907590184</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>19304.0284119565</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.270688984612663</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>186.5043581290274</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>19304.0284119565</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>198.03180914835465</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$50,A12,'Species'!$U$2:$U$50))</x:f>
-        <x:v>3822811.6702709855</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.270688984612663</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>186.5043581290274</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>3600285.428276455</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>222526.24199453043</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0618079445165156</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.061807944516515514</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>31470.7128253108</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.139840861121661</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1379.8785419419437</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>31470.7128253108</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1893.099177804705</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$50,A13,'Species'!$U$2:$U$50))</x:f>
-        <x:v>59577180.57452386</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.139840861121661</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1379.8785419419437</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>43425761.32726349</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>16151419.24726037</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.3719317463553646</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.3719317463553647</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>21.3212787964</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.53</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>33.88441561392024</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>21.3212787964</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$50,A14,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>722.4590721574828</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.53</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>33.88441561392024</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
-        <x:v>722.4590721574828</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>60049.6604650827</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.2628374408276537</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>18.31628703832312</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>60049.6604650827</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>22.631750747897748</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$50,A15,'Species'!$U$2:$U$50))</x:f>
-        <x:v>1359028.9481416412</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.2628374408276537</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>18.31628703832312</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>1099886.8176322987</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>259142.13050934253</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2356079974366743</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.23560799743667435</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>2.7387136433</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>199.52623149688787</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>2.7387136433</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>199.52623149688787</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$50,A16,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>546.445212396761</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.3</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>199.52623149688787</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>546.445212396761</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>0.7976928643</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.538202885014826</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>345.30501435651496</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>0.7976928643</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>359.5288117838723</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$50,A17,'Species'!$U$2:$U$50))</x:f>
-        <x:v>286.7935676702527</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.538202885014826</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>345.30501435651496</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>275.447345959201</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>11.346221711051669</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0411919805273138</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.04119198052731377</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>114.2617895825</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.8994417011349722</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>793.3077575050148</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>114.2617895825</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>804.4590624069095</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$50,A18,'Species'!$U$2:$U$50))</x:f>
-        <x:v>91918.93211647353</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.8994417011349722</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>793.3077575050148</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>90644.76406220294</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>1274.1680542705872</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0140567198497668</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.014056719849766698</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>426851.311182635</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.072915262855542</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>118.2810749698046</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>426851.311182635</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>118.99846715087523</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$50,A19,'Species'!$U$2:$U$50))</x:f>
-        <x:v>50794651.73207481</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.072915262855542</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>118.2810749698046</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>50488431.93895265</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>306219.7931221649</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.006065147626142</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.006065147626141887</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>2.9348711767</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>2.9348711767</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$50,A20,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>378.0846477660875</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>378.0846477660875</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>8.2348084514</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.21</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>162.18100973589299</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>8.2348084514</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>162.18100973589299</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$50,A21,'Species'!$U$2:$U$50))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1335.5295496297172</x:v>
       </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.21</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>162.18100973589299</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>1335.5295496297172</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re606239c82f74c17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6acb1508d0ea4731"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6006,7 +4767,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6105,7 +4866,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>164051844.89863747</x:v>
+        <x:v>154964279.53989428</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6119,7 +4880,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>164051844.89863753</x:v>
+        <x:v>147071763.1699224</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6133,7 +4894,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-2.9802322387695312e-8</x:v>
+        <x:v>-9087565.35874322</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6147,7 +4908,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-16980081.728715092</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6158,9 +4919,9 @@
         <x:v>EEZ_794</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6172,47 +4933,19 @@
         <x:v>EEZ_794</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_794</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_794</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea863f9c6f144d6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd17ae30691874a80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6259,7 +4992,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
